--- a/docs/TD sheet.xlsx
+++ b/docs/TD sheet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="255">
   <si>
     <t>Unit name</t>
   </si>
@@ -45,6 +45,9 @@
     <t>Cost (force)</t>
   </si>
   <si>
+    <t>Faction</t>
+  </si>
+  <si>
     <t>Ugrade paths 1st 3</t>
   </si>
   <si>
@@ -72,6 +75,9 @@
     <t>Heavy</t>
   </si>
   <si>
+    <t>Underworld network</t>
+  </si>
+  <si>
     <t>Damage +5%</t>
   </si>
   <si>
@@ -237,12 +243,12 @@
     <t>triggers a tick of all status effects on hit. (doesnt effect duration)</t>
   </si>
   <si>
+    <t>Ashigaru</t>
+  </si>
+  <si>
     <t>Laisung Collective</t>
   </si>
   <si>
-    <t>Ashigaru</t>
-  </si>
-  <si>
     <t>force per kill +1</t>
   </si>
   <si>
@@ -363,7 +369,7 @@
     <t>Bonus 2</t>
   </si>
   <si>
-    <t>Sewer Rats</t>
+    <t>Underworld Network</t>
   </si>
   <si>
     <t>all % chance to activate abilities trigger at a 5% higher rate</t>
@@ -553,9 +559,6 @@
   </si>
   <si>
     <t>poison</t>
-  </si>
-  <si>
-    <t>sewer rats</t>
   </si>
   <si>
     <t>Molotov cocktail</t>
@@ -1078,13 +1081,14 @@
     <col customWidth="1" min="6" max="6" width="9.5"/>
     <col customWidth="1" min="7" max="8" width="10.25"/>
     <col customWidth="1" min="9" max="9" width="4.75"/>
-    <col customWidth="1" min="10" max="10" width="26.63"/>
-    <col customWidth="1" min="11" max="11" width="16.88"/>
-    <col customWidth="1" min="12" max="12" width="28.0"/>
-    <col customWidth="1" min="13" max="13" width="21.13"/>
-    <col customWidth="1" min="14" max="14" width="30.75"/>
-    <col customWidth="1" min="15" max="15" width="18.38"/>
-    <col customWidth="1" min="16" max="16" width="11.5"/>
+    <col customWidth="1" min="10" max="10" width="7.0"/>
+    <col customWidth="1" min="11" max="11" width="26.63"/>
+    <col customWidth="1" min="12" max="12" width="16.88"/>
+    <col customWidth="1" min="13" max="13" width="28.0"/>
+    <col customWidth="1" min="14" max="14" width="21.13"/>
+    <col customWidth="1" min="15" max="15" width="30.75"/>
+    <col customWidth="1" min="16" max="16" width="18.38"/>
+    <col customWidth="1" min="17" max="17" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1118,7 +1122,7 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1136,10 +1140,13 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3">
         <v>-0.05</v>
@@ -1160,70 +1167,73 @@
         <v>-0.05</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="1">
         <v>9.0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="J4" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="1">
         <v>0.0</v>
@@ -1248,64 +1258,67 @@
         <v>30.0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="K7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="K8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="J7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="J8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3">
         <v>-0.35</v>
@@ -1326,70 +1339,73 @@
         <v>0.25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="1">
         <v>25.0</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="11">
-      <c r="J11" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="K11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="12">
-      <c r="J12" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14" s="3">
         <v>0.05</v>
@@ -1414,64 +1430,67 @@
         <v>15.0</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="15">
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="O15" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16">
-      <c r="J16" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B18" s="3">
         <v>0.1</v>
@@ -1492,75 +1511,73 @@
         <v>-0.25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I18" s="1">
         <v>35.0</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="19">
-      <c r="J19" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="K19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="20">
-      <c r="J20" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>73</v>
+        <v>35</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="1">
         <v>0.0</v>
@@ -1581,70 +1598,73 @@
         <v>0.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I22" s="1">
         <v>15.0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="K23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="J23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>80</v>
+      <c r="M23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="24">
-      <c r="J24" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="K24" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B26" s="3">
         <v>0.05</v>
@@ -1665,43 +1685,46 @@
         <v>0.05</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I26" s="1">
         <v>28.0</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
     </row>
     <row r="28">
-      <c r="J28" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="K28" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B30" s="3">
         <v>0.25</v>
@@ -1722,70 +1745,73 @@
         <v>-0.1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I30" s="1">
         <v>40.0</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>90</v>
+        <v>22</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="P30" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="P30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="31">
-      <c r="J31" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="K31" s="1" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="32">
-      <c r="J32" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="K32" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B34" s="1">
         <v>0.0</v>
@@ -1806,65 +1832,68 @@
         <v>0.3</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I34" s="1">
         <v>45.0</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="35">
-      <c r="J35" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="K35" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="36">
-      <c r="J36" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="K36" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1881,17 +1910,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1915,53 +1944,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1998,75 +2027,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E2" s="1">
         <v>35.0</v>
@@ -2087,22 +2116,22 @@
         <v>0.0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R2" s="5">
         <f t="shared" ref="R2:R14" si="1">E2*(1+F2*G2)*I2</f>
@@ -2115,16 +2144,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E3" s="1">
         <v>15.0</v>
@@ -2151,16 +2180,16 @@
         <v>2.0</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R3" s="5">
         <f t="shared" si="1"/>
@@ -2173,16 +2202,16 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E4" s="1">
         <v>15.0</v>
@@ -2203,22 +2232,22 @@
         <v>0.0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" si="1"/>
@@ -2231,16 +2260,16 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E5" s="1">
         <v>40.0</v>
@@ -2267,16 +2296,16 @@
         <v>4.0</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="1"/>
@@ -2289,16 +2318,16 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E6" s="1">
         <v>25.0</v>
@@ -2325,16 +2354,16 @@
         <v>2.0</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O6" s="1">
         <v>30.0</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="1"/>
@@ -2347,16 +2376,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E7" s="1">
         <v>30.0</v>
@@ -2383,13 +2412,13 @@
         <v>3.0</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O7" s="1">
         <v>35.0</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="1"/>
@@ -2402,16 +2431,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E8" s="1">
         <v>20.0</v>
@@ -2438,16 +2467,16 @@
         <v>4.0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O8" s="1">
         <v>45.0</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="1"/>
@@ -2460,16 +2489,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E9" s="1">
         <v>50.0</v>
@@ -2496,16 +2525,16 @@
         <v>4.0</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O9" s="1">
         <v>75.0</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="1"/>
@@ -2518,16 +2547,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E10" s="1">
         <v>80.0</v>
@@ -2554,16 +2583,16 @@
         <v>5.0</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O10" s="1">
         <v>80.0</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="1"/>
@@ -2576,16 +2605,16 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E11" s="1">
         <v>30.0</v>
@@ -2606,22 +2635,22 @@
         <v>0.2</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O11" s="1">
         <v>50.0</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="1"/>
@@ -2634,16 +2663,16 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E12" s="1">
         <v>90.0</v>
@@ -2670,16 +2699,16 @@
         <v>2.0</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O12" s="1">
         <v>80.0</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="1"/>
@@ -2692,16 +2721,16 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E13" s="1">
         <v>30.0</v>
@@ -2728,16 +2757,16 @@
         <v>10.0</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O13" s="1">
         <v>110.0</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="R13" s="5">
         <f t="shared" si="1"/>
@@ -2750,16 +2779,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E14" s="1">
         <v>100.0</v>
@@ -2780,22 +2809,22 @@
         <v>0.4</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O14" s="1">
         <v>120.0</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="R14" s="5">
         <f t="shared" si="1"/>
@@ -2808,16 +2837,16 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E16" s="1">
         <v>65.0</v>
@@ -2844,16 +2873,16 @@
         <v>3.0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O16" s="1">
         <v>180.0</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R16" s="5">
         <f>E16*(1+F16*G16)*I16</f>
@@ -2866,16 +2895,16 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E18" s="1">
         <v>300.0</v>
@@ -2902,13 +2931,13 @@
         <v>2.0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="O18" s="1">
         <v>300.0</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="R18" s="5">
         <f>E18*(1+F18*G18)*I18</f>
@@ -2921,21 +2950,21 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E22" s="1">
         <v>5.0</v>
@@ -2962,19 +2991,19 @@
         <v>1.2</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O22" s="1">
         <v>35.0</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="R22" s="5">
         <f t="shared" ref="R22:R45" si="3">E22*(1+F22*G22)*I22</f>
@@ -2997,16 +3026,16 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E24" s="1">
         <v>60.0</v>
@@ -3033,19 +3062,19 @@
         <v>2.0</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O24" s="1">
         <v>75.0</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="R24" s="5">
         <f t="shared" si="3"/>
@@ -3068,16 +3097,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E26" s="1">
         <v>40.0</v>
@@ -3098,25 +3127,25 @@
         <v>0.25</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O26" s="1">
         <v>60.0</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="R26" s="5">
         <f t="shared" si="3"/>
@@ -3129,16 +3158,16 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E27" s="1">
         <v>50.0</v>
@@ -3159,25 +3188,25 @@
         <v>0.1</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O27" s="1">
         <v>70.0</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="R27" s="5">
         <f t="shared" si="3"/>
@@ -3190,16 +3219,16 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E28" s="1">
         <v>100.0</v>
@@ -3226,19 +3255,19 @@
         <v>3.0</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O28" s="1">
         <v>250.0</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="R28" s="5">
         <f t="shared" si="3"/>
@@ -3331,7 +3360,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R37" s="5">
         <f t="shared" si="3"/>
@@ -3344,16 +3373,16 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E38" s="1">
         <v>120.0</v>
@@ -3380,19 +3409,19 @@
         <v>5.0</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O38" s="1">
         <v>35.0</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R38" s="5">
         <f t="shared" si="3"/>
@@ -3425,16 +3454,16 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E41" s="1">
         <v>80.0</v>
@@ -3455,25 +3484,25 @@
         <v>0.15</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O41" s="1">
         <v>70.0</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R41" s="5">
         <f t="shared" si="3"/>
@@ -3543,42 +3572,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G2" s="1">
         <v>40.0</v>
@@ -3586,13 +3615,13 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G4" s="1">
         <v>35.0</v>
@@ -3600,13 +3629,13 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G5" s="1">
         <v>45.0</v>
@@ -3614,33 +3643,33 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G6" s="1">
         <v>50.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G7" s="1">
         <v>60.0</v>
@@ -3648,16 +3677,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G8" s="1">
         <v>100.0</v>
@@ -3665,16 +3694,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G10" s="1">
         <v>140.0</v>
@@ -3704,48 +3733,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G2" s="1">
         <v>30.0</v>
@@ -3753,22 +3782,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G3" s="1">
         <v>32.0</v>
@@ -3776,22 +3805,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G4" s="1">
         <v>35.0</v>
@@ -3799,22 +3828,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G5" s="1">
         <v>40.0</v>
@@ -3822,22 +3851,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G6" s="1">
         <v>50.0</v>
@@ -3845,22 +3874,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G7" s="1">
         <v>50.0</v>
@@ -3868,16 +3897,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G8" s="1">
         <v>50.0</v>
@@ -3885,22 +3914,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G9" s="1">
         <v>70.0</v>
@@ -3908,16 +3937,16 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G10" s="1">
         <v>65.0</v>
@@ -3925,13 +3954,13 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G11" s="1">
         <v>70.0</v>
@@ -3939,19 +3968,19 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G12" s="1">
         <v>95.0</v>
@@ -3959,22 +3988,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G13" s="1">
         <v>180.0</v>
